--- a/словари/взаимоотношения.xlsx
+++ b/словари/взаимоотношения.xlsx
@@ -5,16 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E484AF-F775-44B3-B27E-DAC991EA8440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E144E3FE-FA97-4E8D-BC81-836266758019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
     <sheet name="Неизменные" sheetId="2" r:id="rId2"/>
+    <sheet name="неизменные_длинные" sheetId="3" r:id="rId3"/>
+    <sheet name="ошибки" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Этот формат отношений похож</t>
   </si>
@@ -107,6 +109,69 @@
   </si>
   <si>
     <t>трёх-звёздочной харчёвни для дворян</t>
+  </si>
+  <si>
+    <t>весь «заимствованный» материал был серьёзно изменён</t>
+  </si>
+  <si>
+    <t>всё «заимствованное» сырьё было сильно изменено</t>
+  </si>
+  <si>
+    <t>принимает её без аннексий и контрибуций</t>
+  </si>
+  <si>
+    <t>принимает его без насильного захвата земли и требований денежных выплат с проигравших</t>
+  </si>
+  <si>
+    <t>Пик влияния и распространенности этих интеллектуалок (в них еще много от снобок-эпатажниц) пришелся</t>
+  </si>
+  <si>
+    <t>Высшая точка влияния и распространенности этих учёных женщин (в них ещё много от само-званок-раздорниц) пришлась</t>
+  </si>
+  <si>
+    <t>съездить компанией (его университетские</t>
+  </si>
+  <si>
+    <t>съездить содружеством (его одно-учные</t>
+  </si>
+  <si>
+    <t>бирюков</t>
+  </si>
+  <si>
+    <t>по скайпу, телефону</t>
+  </si>
+  <si>
+    <t>по скайпу, так как по телефону</t>
+  </si>
+  <si>
+    <t>было какое-то рабо-владельческое обособленное закрытое вероучение</t>
+  </si>
+  <si>
+    <t>была какая-то тоталитарная секта</t>
+  </si>
+  <si>
+    <t>Кстати, пара, где</t>
+  </si>
+  <si>
+    <t>Кстати, семья, где</t>
+  </si>
+  <si>
+    <t>хороших, крепких парах</t>
+  </si>
+  <si>
+    <t>хороших, крепких семьях</t>
+  </si>
+  <si>
+    <t>фон в паре (и семье)</t>
+  </si>
+  <si>
+    <t>фон в семье</t>
+  </si>
+  <si>
+    <t>неблагоприятный эмоциональный фон в паре</t>
+  </si>
+  <si>
+    <t>неблагоприятная чувственная обстановка в семье</t>
   </si>
 </sst>
 </file>
@@ -424,14 +489,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="59.140625" customWidth="1"/>
-    <col min="2" max="2" width="52.5703125" customWidth="1"/>
+    <col min="1" max="1" width="59.1796875" customWidth="1"/>
+    <col min="2" max="2" width="52.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,7 +504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -447,7 +512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -455,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -463,7 +528,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -471,7 +536,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -479,7 +544,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -487,7 +552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -495,12 +560,68 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -510,14 +631,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4548B0D-7D71-4248-BE5A-4CF5325314DF}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="77.7109375" customWidth="1"/>
-    <col min="2" max="2" width="65.7109375" customWidth="1"/>
+    <col min="1" max="1" width="77.7265625" customWidth="1"/>
+    <col min="2" max="2" width="65.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -525,7 +646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -533,7 +654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -541,12 +662,69 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C072C4D1-91DA-437B-AC9A-0295F76AE4C7}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="99.81640625" customWidth="1"/>
+    <col min="2" max="2" width="117.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7090E7B8-19A4-4D2A-9791-4EE552A78DF4}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.6328125" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/словари/взаимоотношения.xlsx
+++ b/словари/взаимоотношения.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E144E3FE-FA97-4E8D-BC81-836266758019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FB05E9-3500-435D-ADC6-722A91C62E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/взаимоотношения.xlsx
+++ b/словари/взаимоотношения.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FB05E9-3500-435D-ADC6-722A91C62E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964CED3A-5B77-4800-9C07-306584220172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -489,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="59.1796875" customWidth="1"/>
@@ -498,106 +498,106 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -610,28 +610,23 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B16">
+    <sortCondition ref="A1:A16"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4548B0D-7D71-4248-BE5A-4CF5325314DF}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="77.7265625" customWidth="1"/>
@@ -676,6 +671,14 @@
       </c>
       <c r="B5" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
